--- a/coding/output/output_cycle.xlsx
+++ b/coding/output/output_cycle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dirkb\Documents\GitHub\Modellierungsseminar-Firestation\coding\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{420C34AA-FF21-40E8-9122-59BACA14E885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB8ACD9-6678-4A23-8ED5-C7184003A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FBFD2000-7869-4467-9A00-A335B650FC49}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{FBFD2000-7869-4467-9A00-A335B650FC49}"/>
   </bookViews>
   <sheets>
     <sheet name="output_cycle" sheetId="1" r:id="rId1"/>
@@ -610,28 +610,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -656,14 +635,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1634,14 +1620,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:G21">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="[00day">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="[freeDay_:-)_]">
+      <formula>NOT(ISERROR(SEARCH("[freeDay_:-)_]",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="[night">
+      <formula>NOT(ISERROR(SEARCH("[night",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="[00day">
       <formula>NOT(ISERROR(SEARCH("[00day",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="[night">
-      <formula>NOT(ISERROR(SEARCH("[night",A4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="[freeDay_:-)_]">
-      <formula>NOT(ISERROR(SEARCH("[freeDay_:-)_]",A4)))</formula>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="reserveShift">
+      <formula>NOT(ISERROR(SEARCH("reserveShift",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/coding/output/output_cycle.xlsx
+++ b/coding/output/output_cycle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dirkb\Documents\GitHub\Modellierungsseminar-Firestation\coding\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB8ACD9-6678-4A23-8ED5-C7184003A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65EC758-59AD-43C4-BE9E-4D599E02973D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{FBFD2000-7869-4467-9A00-A335B650FC49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FBFD2000-7869-4467-9A00-A335B650FC49}"/>
   </bookViews>
   <sheets>
     <sheet name="output_cycle" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +220,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="33">
@@ -563,8 +569,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -610,7 +617,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -636,27 +643,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -991,646 +977,647 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392839E4-2739-46E3-AB50-81885D089FB2}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>48</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>8</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>36</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>-4</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>50</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>10</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
         <v>42</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>38</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>-2</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>28</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>-12</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1">
         <v>20</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-20</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11">
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1">
         <v>44</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>4</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>38</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>-2</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>38</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-2</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1">
         <v>44</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>4</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="1">
         <v>40</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>0</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>52</v>
       </c>
-      <c r="I16">
-        <v>12</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="I16" s="1">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>38</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-2</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
         <v>42</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>2</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1">
         <v>28</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-12</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>38</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-2</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>46</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>6</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:G21">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="[freeDay_:-)_]">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="reserveShift">
+      <formula>NOT(ISERROR(SEARCH("reserveShift",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="[freeDay_:-)_]">
       <formula>NOT(ISERROR(SEARCH("[freeDay_:-)_]",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="[night">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="[night">
       <formula>NOT(ISERROR(SEARCH("[night",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="[00day">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="[00day">
       <formula>NOT(ISERROR(SEARCH("[00day",A4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="reserveShift">
-      <formula>NOT(ISERROR(SEARCH("reserveShift",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
